--- a/git操作.xlsx
+++ b/git操作.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE53BFA-57DB-46DC-94F9-222007AB7326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB0DF15-EA2D-40F3-9751-0163BACB437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="git分支操作" sheetId="1" r:id="rId1"/>
-    <sheet name="svn操作" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId3"/>
-    <sheet name="低功耗标志位" sheetId="3" r:id="rId4"/>
-    <sheet name="RS485" sheetId="4" r:id="rId5"/>
-    <sheet name="按键" sheetId="5" r:id="rId6"/>
-    <sheet name="灯控" sheetId="7" r:id="rId7"/>
-    <sheet name="can" sheetId="10" r:id="rId8"/>
-    <sheet name="负债" sheetId="6" state="hidden" r:id="rId9"/>
+    <sheet name="20260417 git" sheetId="11" r:id="rId2"/>
+    <sheet name="svn操作" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId4"/>
+    <sheet name="低功耗标志位" sheetId="3" r:id="rId5"/>
+    <sheet name="RS485" sheetId="4" r:id="rId6"/>
+    <sheet name="按键" sheetId="5" r:id="rId7"/>
+    <sheet name="灯控" sheetId="7" r:id="rId8"/>
+    <sheet name="can" sheetId="10" r:id="rId9"/>
+    <sheet name="负债" sheetId="6" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16844" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16873" uniqueCount="370">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2341,6 +2342,100 @@
     <t>正常commit 后 pull 如果分支没从冲突  直接commit  如果有冲突 那就解决冲突 commit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>步骤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本地仓库初始化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git remote add origin https://github.com/masterwey/2026.git</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测远程仓库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git remote -v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>origin  https://github.com/你的用户名/仓库名.git (fetch)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>origin  https://github.com/你的用户名/仓库名.git (push)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看本地状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加本地修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git add .</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提交本地修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git commit -m "first name"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一次提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git push -u origin main</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非第一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git push 或者git pull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘-u 是会将本地的 main 分支与远程的 origin/main 分支关联起来，并记住这个对应关系
+-u  就是--set-upstream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新建远程仓库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git上新建文件夹2026 复制git地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git branch -M main</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制本地分支的名字为main(因为默认是master)
+’-M 是 --move --force 的缩写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制修改本地分支名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2350,7 +2445,7 @@
     <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2570,6 +2665,21 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2636,7 +2746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2731,6 +2841,27 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -52861,1250 +52992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CE3146-89A6-413F-8B1E-5DE55F7871A3}">
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="4.9140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="3" max="3" width="72.9140625" customWidth="1"/>
-    <col min="4" max="4" width="50.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1">
-        <v>4</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="1">
-        <v>5</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1">
-        <v>6</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1">
-        <v>7</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93C59C3-6145-46DB-A56B-9A466B5CDDE9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A1ADA4-E888-4B1E-8CCD-3B1B5F4B269F}">
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="9.08203125" style="1"/>
-    <col min="2" max="2" width="21.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08203125" style="1"/>
-    <col min="5" max="5" width="61.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08203125" style="1"/>
-    <col min="7" max="7" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.08203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="19.149999999999999" customHeight="1">
-      <c r="G2" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="39" customHeight="1">
-      <c r="C3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="42.75" customHeight="1">
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="60" customHeight="1">
-      <c r="C5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16">
-      <c r="E6" s="4"/>
-      <c r="G6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="C11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="C12" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="C13" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="C14" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="C15" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="C16" s="1">
-        <v>485</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="C17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="C18" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="C19" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1">
-        <v>2</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="C23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>3</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="C27" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="C28" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="C29" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="C30" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="C31" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="C32" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC7B595-80EB-432C-BC59-761EBA693BD0}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F062A636-3825-4A0D-A662-FF46A7804170}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="13"/>
-  <cols>
-    <col min="1" max="1" width="10.4140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="74.1640625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="15.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.08203125" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="6" customFormat="1">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="6" customFormat="1">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="6" customFormat="1">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="6" customFormat="1">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="6" customFormat="1">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="6" customFormat="1">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="6" customFormat="1">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.5">
-      <c r="A18" s="5">
-        <v>1</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.5">
-      <c r="A19" s="5">
-        <v>2</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.5">
-      <c r="A20" s="5">
-        <v>3</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C39F64-EB6B-443B-8141-404518C7E464}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="9.08203125" style="1"/>
-    <col min="2" max="2" width="11.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.4140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.08203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="B2" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="B3" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="B4" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97964471-DF80-4FFC-9570-FCF40A6A4558}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="9.08203125" style="1"/>
-    <col min="2" max="2" width="18.4140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.08203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB2E583-6864-47AF-B212-8060A1438A79}">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
@@ -54438,4 +53326,1416 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F422C4-2D38-418C-B862-4AF1A041E07B}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="35"/>
+    <col min="2" max="2" width="18.25" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.33203125" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" style="35" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="35"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="40">
+        <v>1</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.5">
+      <c r="A3" s="40">
+        <v>2</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.5">
+      <c r="A4" s="40">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="41">
+        <v>4</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="35" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="40">
+        <v>5</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="40">
+        <v>6</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="40">
+        <v>7</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42">
+      <c r="A11" s="40">
+        <v>8</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="56">
+      <c r="A12" s="40">
+        <v>9</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="40">
+        <v>10</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>362</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CE3146-89A6-413F-8B1E-5DE55F7871A3}">
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="4.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="72.9140625" customWidth="1"/>
+    <col min="4" max="4" width="50.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
+        <v>2</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1">
+        <v>6</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1">
+        <v>7</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93C59C3-6145-46DB-A56B-9A466B5CDDE9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A1ADA4-E888-4B1E-8CCD-3B1B5F4B269F}">
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="9.08203125" style="1"/>
+    <col min="2" max="2" width="21.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08203125" style="1"/>
+    <col min="5" max="5" width="61.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08203125" style="1"/>
+    <col min="7" max="7" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.08203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="G2" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="39" customHeight="1">
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="42.75" customHeight="1">
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60" customHeight="1">
+      <c r="C5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16">
+      <c r="E6" s="4"/>
+      <c r="G6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="C11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="C12" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="C14" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="C15" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="C16" s="1">
+        <v>485</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="C17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="C18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>2</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="C22" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="C23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="C27" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="C28" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="C29" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="C30" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="C31" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC7B595-80EB-432C-BC59-761EBA693BD0}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F062A636-3825-4A0D-A662-FF46A7804170}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="10.4140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="74.1640625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="15.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.08203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="6" customFormat="1">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="6" customFormat="1">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="6" customFormat="1">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="6" customFormat="1">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="6" customFormat="1">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="6" customFormat="1">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="6" customFormat="1">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.5">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.5">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.5">
+      <c r="A20" s="5">
+        <v>3</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C39F64-EB6B-443B-8141-404518C7E464}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="9.08203125" style="1"/>
+    <col min="2" max="2" width="11.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.4140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.08203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="B2" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="B3" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97964471-DF80-4FFC-9570-FCF40A6A4558}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="9.08203125" style="1"/>
+    <col min="2" max="2" width="18.4140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.08203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>